--- a/data/Data_for_figures_4results/Result3_intensity_Dominance Score_S-T.xlsx
+++ b/data/Data_for_figures_4results/Result3_intensity_Dominance Score_S-T.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\State_SDG\Github\SDG_Interactions-driven-by-Urban_Typologies\data\Data_for_figures_4results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\City SDG paper\data for governance capacity\WGI_data_072026\1_Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3EA40E6-29ED-42D5-BA6E-9F3C759B12CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88BD2F56-0C46-4150-BE7D-BFB91510FC26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1536" windowWidth="15648" windowHeight="11316" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10488" yWindow="1860" windowWidth="15048" windowHeight="9024" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$121</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -105,8 +108,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -134,8 +145,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -415,27 +430,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FF49B95-A160-47B8-BA10-DBC8A98E7270}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F121"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>20</v>
       </c>
     </row>
@@ -533,7 +548,7 @@
         <v>-2.1907110402646111E-2</v>
       </c>
       <c r="E6">
-        <v>-0.1791847864379868</v>
+        <v>-0.1106170859981648</v>
       </c>
       <c r="F6">
         <v>8.3500215732536132E-2</v>
@@ -633,2209 +648,2209 @@
         <v>3.9457751992410542E-2</v>
       </c>
       <c r="E11">
-        <v>8.7953531782536648E-2</v>
+        <v>3.9982060759796878E-2</v>
       </c>
       <c r="F11">
         <v>7.5152561170532428E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12">
+    <row r="12" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="2">
         <v>3.951583002435255E-2</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="2">
         <v>5.6175637289547713E-2</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="2">
         <v>2.074743845288464E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13">
+    <row r="13" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="2">
         <v>-2.0244519074498021E-2</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="2">
         <v>-0.21612197885837239</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="2">
         <v>-3.3135835213793527E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14">
+    <row r="14" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="2">
         <v>5.0070584829229367E-2</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="2">
         <v>3.4633318181659482E-2</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="2">
         <v>8.8622641989339265E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15">
+    <row r="15" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="2">
         <v>0.10705138156729629</v>
       </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16">
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="2">
         <v>4.0291793272140518E-2</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="2">
         <v>7.8270882543196738E-2</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="2">
         <v>8.3226088672199092E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17">
+    <row r="17" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="2">
         <v>0.11491101491101489</v>
       </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18">
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="2">
         <v>0.1960592317735175</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="2">
         <v>8.4221995751564777E-2</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="2">
         <v>0.1379533631634472</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19">
+    <row r="19" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="2">
         <v>6.0422380000977771E-2</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="2">
         <v>0.1137254901960784</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="2">
         <v>-3.4273283193189411E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20">
+    <row r="20" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="2">
         <v>-4.2512425845759177E-2</v>
       </c>
-      <c r="E20">
-        <v>-6.4753512747578623E-2</v>
-      </c>
-      <c r="F20">
-        <v>7.5542871402030712E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21">
+      <c r="E20" s="2">
+        <v>6.4753512747578623E-2</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.1604982116978759</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
+      <c r="D21" s="2">
+        <v>0</v>
+      </c>
+      <c r="E21" s="2">
         <v>0.13562091503267981</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="2">
         <v>-7.7989983872336813E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22">
+    <row r="22" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22">
+      <c r="D22" s="2">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2">
         <v>8.3006535947712415E-2</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="2">
         <v>4.4910657568765118E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23">
+    <row r="23" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="2">
         <v>0.1371324105064767</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="2">
         <v>7.3856209150326785E-2</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="2">
         <v>3.7942449707155587E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24">
+    <row r="24" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="2">
         <v>0.15012788149478121</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="2">
         <v>0.21824779291330759</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="2">
         <v>0.1247291190180714</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25">
+    <row r="25" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D25">
-        <v>4.0459135213800068E-2</v>
-      </c>
-      <c r="E25">
+      <c r="D25" s="2">
+        <v>8.856880332346817E-2</v>
+      </c>
+      <c r="E25" s="2">
         <v>3.6267185335900107E-2</v>
       </c>
-      <c r="F25">
-        <v>-2.3458110516934041E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26">
+      <c r="F25" s="2">
+        <v>2.3458110516934041E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="2">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="2">
         <v>7.7214927535474737E-2</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="2">
         <v>7.8926637349202772E-2</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="2">
         <v>-4.3078138293032781E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27">
+    <row r="27" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
         <v>26</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
-      <c r="E27">
+      <c r="D27" s="2">
+        <v>0</v>
+      </c>
+      <c r="E27" s="2">
         <v>-6.4052287581699341E-2</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="2">
         <v>5.2467780711839412E-4</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28">
+    <row r="28" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
         <v>27</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="2">
         <v>0.1097803431136764</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="2">
         <v>1.4877682912866411E-2</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="2">
         <v>0.1194126135302606</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29">
+    <row r="29" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
         <v>28</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="2">
         <v>5.0709475709475711E-2</v>
       </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-      <c r="F29">
+      <c r="E29" s="2">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2">
         <v>8.3447924624395209E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30">
+    <row r="30" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="2">
         <v>0.1962962962962963</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="2">
         <v>7.1241830065359474E-2</v>
       </c>
-      <c r="F30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31">
+      <c r="F30" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="2">
         <v>0.22205383175801491</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="2">
         <v>0.25894317240790038</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="2">
         <v>0.19116724310940411</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32">
+    <row r="32" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="2">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="2">
         <v>6.1662177046107887E-2</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="2">
         <v>0.1103991596638656</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="2">
         <v>1.5627388778362662E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33">
+    <row r="33" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="2">
         <v>32</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="2">
         <v>-1.5070879888401979E-3</v>
       </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-      <c r="F33">
-        <v>9.3062499307627125E-2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34">
+      <c r="E33" s="2">
+        <v>0</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.1365034204436531</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="2">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="2">
         <v>8.8828115391379608E-3</v>
       </c>
-      <c r="E34">
+      <c r="E34" s="2">
         <v>5.527929823771667E-2</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="2">
         <v>1.059704531806915E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35">
+    <row r="35" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="2">
         <v>34</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="2">
         <v>4.0219952577081317E-2</v>
       </c>
-      <c r="E35">
+      <c r="E35" s="2">
         <v>5.5376232942554587E-2</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="2">
         <v>9.5274210177442448E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36">
+    <row r="36" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="2">
         <v>35</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="2">
         <v>9.6697758772530146E-2</v>
       </c>
-      <c r="E36">
+      <c r="E36" s="2">
         <v>0.16287262606651001</v>
       </c>
-      <c r="F36">
+      <c r="F36" s="2">
         <v>0.1035258739953188</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37">
+    <row r="37" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="2">
         <v>36</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="2">
         <v>0.21708888555600081</v>
       </c>
-      <c r="E37">
+      <c r="E37" s="2">
         <v>5.3747092076484287E-2</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="2">
         <v>0.20505777809391129</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38">
+    <row r="38" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="2">
         <v>37</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D38">
-        <v>5.6911035430883217E-2</v>
-      </c>
-      <c r="E38">
-        <v>-2.632025868539203E-2</v>
-      </c>
-      <c r="F38">
-        <v>1.278466093857988E-2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39">
+      <c r="D38" s="2">
+        <v>3.5923878695449822E-2</v>
+      </c>
+      <c r="E38" s="2">
+        <v>-5.5080909801849029E-2</v>
+      </c>
+      <c r="F38" s="2">
+        <v>3.9704698441535791E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="2">
         <v>38</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="2">
         <v>9.9887048787566171E-2</v>
       </c>
-      <c r="E39">
-        <v>0</v>
-      </c>
-      <c r="F39">
+      <c r="E39" s="2">
+        <v>0</v>
+      </c>
+      <c r="F39" s="2">
         <v>-8.2843903295483218E-3</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40">
+    <row r="40" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="2">
         <v>39</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="2">
         <v>-3.2493090204517898E-2</v>
       </c>
-      <c r="E40">
+      <c r="E40" s="2">
         <v>-0.1570028011204482</v>
       </c>
-      <c r="F40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41">
+      <c r="F40" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="2">
         <v>40</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="2">
         <v>0.13604741806991011</v>
       </c>
-      <c r="E41">
+      <c r="E41" s="2">
         <v>5.2010403121040362E-2</v>
       </c>
-      <c r="F41">
+      <c r="F41" s="2">
         <v>7.2807304740077836E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42">
+    <row r="42" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="2">
         <v>41</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="2">
         <v>0.1024582560296846</v>
       </c>
-      <c r="E42">
+      <c r="E42" s="2">
         <v>3.9915966386554619E-2</v>
       </c>
-      <c r="F42">
+      <c r="F42" s="2">
         <v>6.7401506056968249E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43">
+    <row r="43" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="2">
         <v>42</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="2">
         <v>0.15093400896484929</v>
       </c>
-      <c r="E43">
+      <c r="E43" s="2">
         <v>0.11969555212828691</v>
       </c>
-      <c r="F43">
+      <c r="F43" s="2">
         <v>3.9317545199898142E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44">
+    <row r="44" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="2">
         <v>43</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D44">
-        <v>0</v>
-      </c>
-      <c r="E44">
+      <c r="D44" s="2">
+        <v>0</v>
+      </c>
+      <c r="E44" s="2">
         <v>0.1142156862745098</v>
       </c>
-      <c r="F44">
+      <c r="F44" s="2">
         <v>5.780155546133673E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45">
+    <row r="45" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="2">
         <v>44</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D45">
-        <v>1.623075528969296E-2</v>
-      </c>
-      <c r="E45">
-        <v>-3.6899763477548558E-2</v>
-      </c>
-      <c r="F45">
-        <v>6.0425366509947821E-2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46">
+      <c r="D45" s="2">
+        <v>-9.1122530181467848E-2</v>
+      </c>
+      <c r="E45" s="2">
+        <v>0.15196464870288909</v>
+      </c>
+      <c r="F45" s="2">
+        <v>-1.202072966956288E-3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="2">
         <v>45</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="2">
         <v>2.9395141895141891E-2</v>
       </c>
-      <c r="E46">
-        <v>0</v>
-      </c>
-      <c r="F46">
+      <c r="E46" s="2">
+        <v>0</v>
+      </c>
+      <c r="F46" s="2">
         <v>3.4494613898517441E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47">
+    <row r="47" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="2">
         <v>46</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="2">
         <v>-8.1061307554890105E-2</v>
       </c>
-      <c r="E47">
-        <v>0</v>
-      </c>
-      <c r="F47">
+      <c r="E47" s="2">
+        <v>0</v>
+      </c>
+      <c r="F47" s="2">
         <v>-2.9396066772282629E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48">
+    <row r="48" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="2">
         <v>47</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="2">
         <v>8.8112014830882615E-2</v>
       </c>
-      <c r="E48">
+      <c r="E48" s="2">
         <v>0.1774361082894719</v>
       </c>
-      <c r="F48">
+      <c r="F48" s="2">
         <v>-7.6870966749377295E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49">
+    <row r="49" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="2">
         <v>48</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="2">
         <v>9.7286658594214717E-2</v>
       </c>
-      <c r="E49">
+      <c r="E49" s="2">
         <v>0.14626401595745109</v>
       </c>
-      <c r="F49">
+      <c r="F49" s="2">
         <v>0.1253146326767737</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50">
+    <row r="50" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="2">
         <v>49</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D50">
-        <v>5.8109882345589968E-2</v>
-      </c>
-      <c r="E50">
+      <c r="D50" s="2">
+        <v>9.5967025202732842E-2</v>
+      </c>
+      <c r="E50" s="2">
         <v>-6.2616423476178837E-4</v>
       </c>
-      <c r="F50">
+      <c r="F50" s="2">
         <v>1.1968311270363369E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51">
+    <row r="51" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="2">
         <v>50</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D51">
+      <c r="D51" s="2">
         <v>6.7529748984231364E-2</v>
       </c>
-      <c r="E51">
+      <c r="E51" s="2">
         <v>5.6851594593677141E-2</v>
       </c>
-      <c r="F51">
+      <c r="F51" s="2">
         <v>-4.7386278459787817E-4</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52">
+    <row r="52" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="2">
         <v>51</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="2">
         <v>2.2478396744335261E-2</v>
       </c>
-      <c r="E52">
+      <c r="E52" s="2">
         <v>-5.1470588235294122E-2</v>
       </c>
-      <c r="F52">
+      <c r="F52" s="2">
         <v>-1.815711411144335E-3</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53">
+    <row r="53" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="2">
         <v>52</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="2">
         <v>5.1676344713905489E-2</v>
       </c>
-      <c r="E53">
+      <c r="E53" s="2">
         <v>2.2407702829060901E-5</v>
       </c>
-      <c r="F53">
+      <c r="F53" s="2">
         <v>0.11143603801625521</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54">
+    <row r="54" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="2">
         <v>53</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="2">
         <v>3.5650821226436709E-2</v>
       </c>
-      <c r="E54">
-        <v>0</v>
-      </c>
-      <c r="F54">
+      <c r="E54" s="2">
+        <v>0</v>
+      </c>
+      <c r="F54" s="2">
         <v>5.800091972018219E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55">
+    <row r="55" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="2">
         <v>54</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="2">
         <v>5.8144747605093777E-3</v>
       </c>
-      <c r="E55">
+      <c r="E55" s="2">
         <v>9.3627450980392157E-2</v>
       </c>
-      <c r="F55">
+      <c r="F55" s="2">
         <v>3.7063916475681177E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56">
+    <row r="56" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="2">
         <v>55</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D56">
-        <v>0</v>
-      </c>
-      <c r="E56">
-        <v>0</v>
-      </c>
-      <c r="F56">
-        <v>-0.1142565886055127</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57">
+      <c r="D56" s="2">
+        <v>0</v>
+      </c>
+      <c r="E56" s="2">
+        <v>0</v>
+      </c>
+      <c r="F56" s="2">
+        <v>0.1142565886055127</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="2">
         <v>56</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="2">
         <v>-3.7734487734487732E-2</v>
       </c>
-      <c r="E57">
-        <v>0</v>
-      </c>
-      <c r="F57">
+      <c r="E57" s="2">
+        <v>0</v>
+      </c>
+      <c r="F57" s="2">
         <v>-4.9995755878108818E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58">
+    <row r="58" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="2">
         <v>57</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D58">
-        <v>-1.8630857256091431E-3</v>
-      </c>
-      <c r="E58">
-        <v>0</v>
-      </c>
-      <c r="F58">
-        <v>4.9561732388107897E-2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59">
+      <c r="D58" s="2">
+        <v>-6.8379017849827764E-2</v>
+      </c>
+      <c r="E58" s="2">
+        <v>0</v>
+      </c>
+      <c r="F58" s="2">
+        <v>0.1293562214638545</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="2">
         <v>58</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="2">
         <v>-4.2351566325704582E-2</v>
       </c>
-      <c r="E59">
+      <c r="E59" s="2">
         <v>-5.8134916486780819E-2</v>
       </c>
-      <c r="F59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60">
+      <c r="F59" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="2">
         <v>59</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D60">
-        <v>0</v>
-      </c>
-      <c r="E60">
-        <v>0</v>
-      </c>
-      <c r="F60">
+      <c r="D60" s="2">
+        <v>0</v>
+      </c>
+      <c r="E60" s="2">
+        <v>0</v>
+      </c>
+      <c r="F60" s="2">
         <v>9.5008763964042495E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61">
+    <row r="61" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="2">
         <v>60</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D61">
-        <v>-1.002267487329505E-2</v>
-      </c>
-      <c r="E61">
-        <v>1.729322479210933E-3</v>
-      </c>
-      <c r="F61">
+      <c r="D61" s="2">
+        <v>2.9391836736301379E-2</v>
+      </c>
+      <c r="E61" s="2">
+        <v>-1.729322479210933E-3</v>
+      </c>
+      <c r="F61" s="2">
         <v>2.7389865036923859E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62">
+    <row r="62" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="2">
         <v>61</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D62">
-        <v>-5.979565636710818E-2</v>
-      </c>
-      <c r="E62">
+      <c r="D62" s="2">
+        <v>-6.4443457286758821E-2</v>
+      </c>
+      <c r="E62" s="2">
         <v>7.6943446411982711E-2</v>
       </c>
-      <c r="F62">
+      <c r="F62" s="2">
         <v>-9.2043714786338021E-3</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63">
+    <row r="63" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="2">
         <v>62</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D63">
-        <v>0</v>
-      </c>
-      <c r="E63">
+      <c r="D63" s="2">
+        <v>0</v>
+      </c>
+      <c r="E63" s="2">
         <v>5.7843137254901963E-2</v>
       </c>
-      <c r="F63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64">
+      <c r="F63" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="2">
         <v>63</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="2">
         <v>3.2003657769915358E-2</v>
       </c>
-      <c r="E64">
-        <v>-6.2280481721692912E-2</v>
-      </c>
-      <c r="F64">
-        <v>5.2723404121868857E-2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65">
+      <c r="E64" s="2">
+        <v>6.2280481721692912E-2</v>
+      </c>
+      <c r="F64" s="2">
+        <v>0.15106235260506429</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="2">
         <v>64</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D65">
-        <v>0</v>
-      </c>
-      <c r="E65">
+      <c r="D65" s="2">
+        <v>0</v>
+      </c>
+      <c r="E65" s="2">
         <v>-8.8397486932772329E-2</v>
       </c>
-      <c r="F65">
-        <v>2.6851070935517969E-3</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66">
+      <c r="F65" s="2">
+        <v>0.175517082873344</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="2">
         <v>65</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C66" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D66">
-        <v>-1.5685911823208089E-2</v>
-      </c>
-      <c r="E66">
+      <c r="D66" s="2">
+        <v>-0.1089413128040165</v>
+      </c>
+      <c r="E66" s="2">
         <v>-5.8108590106645493E-2</v>
       </c>
-      <c r="F66">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67">
+      <c r="F66" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="2">
         <v>66</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C67" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D67">
-        <v>0</v>
-      </c>
-      <c r="E67">
-        <v>0</v>
-      </c>
-      <c r="F67">
+      <c r="D67" s="2">
+        <v>0</v>
+      </c>
+      <c r="E67" s="2">
+        <v>0</v>
+      </c>
+      <c r="F67" s="2">
         <v>-0.1198370257193787</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68">
+    <row r="68" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="2">
         <v>67</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C68" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D68">
-        <v>0</v>
-      </c>
-      <c r="E68">
+      <c r="D68" s="2">
+        <v>0</v>
+      </c>
+      <c r="E68" s="2">
         <v>0.1342848977675998</v>
       </c>
-      <c r="F68">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69">
+      <c r="F68" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="2">
         <v>68</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C69" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="2">
         <v>3.111495947361112E-2</v>
       </c>
-      <c r="E69">
-        <v>0</v>
-      </c>
-      <c r="F69">
+      <c r="E69" s="2">
+        <v>0</v>
+      </c>
+      <c r="F69" s="2">
         <v>-5.7892372831934678E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70">
+    <row r="70" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="2">
         <v>69</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C70" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="2">
         <v>3.1361231361231361E-2</v>
       </c>
-      <c r="E70">
+      <c r="E70" s="2">
         <v>5.5964714596689821E-2</v>
       </c>
-      <c r="F70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71">
+      <c r="F70" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="2">
         <v>70</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C71" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="2">
         <v>-1.35958774343442E-2</v>
       </c>
-      <c r="E71">
-        <v>0</v>
-      </c>
-      <c r="F71">
+      <c r="E71" s="2">
+        <v>0</v>
+      </c>
+      <c r="F71" s="2">
         <v>-5.5859434682964088E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72">
+    <row r="72" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="2">
         <v>71</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C72" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D72">
+      <c r="D72" s="2">
         <v>2.6445500956839431E-2</v>
       </c>
-      <c r="E72">
-        <v>0</v>
-      </c>
-      <c r="F72">
+      <c r="E72" s="2">
+        <v>0</v>
+      </c>
+      <c r="F72" s="2">
         <v>6.7837861315137651E-3</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73">
+    <row r="73" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="2">
         <v>72</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C73" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D73">
+      <c r="D73" s="2">
         <v>8.1753911149263281E-2</v>
       </c>
-      <c r="E73">
+      <c r="E73" s="2">
         <v>-6.2930460623373985E-2</v>
       </c>
-      <c r="F73">
+      <c r="F73" s="2">
         <v>3.7695532118865727E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74">
+    <row r="74" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="2">
         <v>73</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C74" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D74">
+      <c r="D74" s="2">
         <v>5.6116722783390582E-5</v>
       </c>
-      <c r="E74">
+      <c r="E74" s="2">
         <v>6.5686274509803924E-2</v>
       </c>
-      <c r="F74">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75">
+      <c r="F74" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="2">
         <v>74</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D75">
-        <v>0</v>
-      </c>
-      <c r="E75">
-        <v>0</v>
-      </c>
-      <c r="F75">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76">
+      <c r="D75" s="2">
+        <v>0</v>
+      </c>
+      <c r="E75" s="2">
+        <v>0</v>
+      </c>
+      <c r="F75" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="2">
         <v>75</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="2">
         <v>6.4991181657848313E-2</v>
       </c>
-      <c r="E76">
-        <v>0</v>
-      </c>
-      <c r="F76">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77">
+      <c r="E76" s="2">
+        <v>0</v>
+      </c>
+      <c r="F76" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="2">
         <v>76</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C77" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D77">
+      <c r="D77" s="2">
         <v>-0.1005162223236943</v>
       </c>
-      <c r="E77">
+      <c r="E77" s="2">
         <v>0.28056004308023691</v>
       </c>
-      <c r="F77">
+      <c r="F77" s="2">
         <v>0.16380193118633679</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78">
+    <row r="78" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="2">
         <v>77</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C78" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D78">
-        <v>0</v>
-      </c>
-      <c r="E78">
-        <v>0</v>
-      </c>
-      <c r="F78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79">
+      <c r="D78" s="2">
+        <v>0</v>
+      </c>
+      <c r="E78" s="2">
+        <v>0</v>
+      </c>
+      <c r="F78" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="2">
         <v>78</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C79" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D79">
+      <c r="D79" s="2">
         <v>3.5233285233285228E-2</v>
       </c>
-      <c r="E79">
-        <v>0</v>
-      </c>
-      <c r="F79">
+      <c r="E79" s="2">
+        <v>0</v>
+      </c>
+      <c r="F79" s="2">
         <v>3.8517557251251951E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80">
+    <row r="80" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="2">
         <v>79</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C80" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D80">
+      <c r="D80" s="2">
         <v>-9.7894407647207034E-3</v>
       </c>
-      <c r="E80">
-        <v>-3.8431372549019613E-2</v>
-      </c>
-      <c r="F80">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81">
+      <c r="E80" s="2">
+        <v>3.8431372549019613E-2</v>
+      </c>
+      <c r="F80" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="2">
         <v>80</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C81" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D81">
+      <c r="D81" s="2">
         <v>1.442977668760957E-2</v>
       </c>
-      <c r="E81">
-        <v>0</v>
-      </c>
-      <c r="F81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82">
+      <c r="E81" s="2">
+        <v>0</v>
+      </c>
+      <c r="F81" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="2">
         <v>81</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C82" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D82">
+      <c r="D82" s="2">
         <v>3.7952284823563047E-2</v>
       </c>
-      <c r="E82">
-        <v>0</v>
-      </c>
-      <c r="F82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83">
+      <c r="E82" s="2">
+        <v>0</v>
+      </c>
+      <c r="F82" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="2">
         <v>82</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C83" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D83">
-        <v>0</v>
-      </c>
-      <c r="E83">
+      <c r="D83" s="2">
+        <v>0</v>
+      </c>
+      <c r="E83" s="2">
         <v>-0.12354264582535671</v>
       </c>
-      <c r="F83">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84">
+      <c r="F83" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="2">
         <v>83</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C84" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D84">
-        <v>0</v>
-      </c>
-      <c r="E84">
-        <v>0</v>
-      </c>
-      <c r="F84">
+      <c r="D84" s="2">
+        <v>0</v>
+      </c>
+      <c r="E84" s="2">
+        <v>0</v>
+      </c>
+      <c r="F84" s="2">
         <v>0.1283223417068077</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85">
+    <row r="85" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="2">
         <v>84</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C85" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D85">
+      <c r="D85" s="2">
         <v>9.1310151717281865E-3</v>
       </c>
-      <c r="E85">
-        <v>0</v>
-      </c>
-      <c r="F85">
+      <c r="E85" s="2">
+        <v>0</v>
+      </c>
+      <c r="F85" s="2">
         <v>0.108210053806319</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86">
+    <row r="86" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="2">
         <v>85</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C86" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D86">
+      <c r="D86" s="2">
         <v>0.15041928170705951</v>
       </c>
-      <c r="E86">
+      <c r="E86" s="2">
         <v>0.19749495572692299</v>
       </c>
-      <c r="F86">
+      <c r="F86" s="2">
         <v>0.21824171001872841</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87">
+    <row r="87" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="2">
         <v>86</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C87" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D87">
+      <c r="D87" s="2">
         <v>7.9094647601783988E-2</v>
       </c>
-      <c r="E87">
+      <c r="E87" s="2">
         <v>0.28575297239738717</v>
       </c>
-      <c r="F87">
+      <c r="F87" s="2">
         <v>9.3642305407011281E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88">
+    <row r="88" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="2">
         <v>87</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C88" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D88">
-        <v>2.456805094703781E-2</v>
-      </c>
-      <c r="E88">
+      <c r="D88" s="2">
+        <v>6.0845107224094093E-2</v>
+      </c>
+      <c r="E88" s="2">
         <v>3.6852277891197528E-2</v>
       </c>
-      <c r="F88">
+      <c r="F88" s="2">
         <v>0.16191354907396499</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89">
+    <row r="89" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="2">
         <v>88</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C89" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D89">
+      <c r="D89" s="2">
         <v>2.0628072900931209E-2</v>
       </c>
-      <c r="E89">
+      <c r="E89" s="2">
         <v>8.1999546602212522E-2</v>
       </c>
-      <c r="F89">
+      <c r="F89" s="2">
         <v>7.3389096528302694E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90">
+    <row r="90" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="2">
         <v>89</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C90" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D90">
-        <v>0</v>
-      </c>
-      <c r="E90">
+      <c r="D90" s="2">
+        <v>0</v>
+      </c>
+      <c r="E90" s="2">
         <v>-0.27434688780893141</v>
       </c>
-      <c r="F90">
+      <c r="F90" s="2">
         <v>0.1021043542090094</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91">
+    <row r="91" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="2">
         <v>90</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C91" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D91">
+      <c r="D91" s="2">
         <v>7.9599297895838195E-2</v>
       </c>
-      <c r="E91">
-        <v>0</v>
-      </c>
-      <c r="F91">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92">
+      <c r="E91" s="2">
+        <v>0</v>
+      </c>
+      <c r="F91" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="2">
         <v>91</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C92" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D92">
-        <v>0</v>
-      </c>
-      <c r="E92">
+      <c r="D92" s="2">
+        <v>0</v>
+      </c>
+      <c r="E92" s="2">
         <v>0.1007126018010428</v>
       </c>
-      <c r="F92">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93">
+      <c r="F92" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="2">
         <v>92</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C93" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D93">
+      <c r="D93" s="2">
         <v>0.1242711247013773</v>
       </c>
-      <c r="E93">
-        <v>0</v>
-      </c>
-      <c r="F93">
+      <c r="E93" s="2">
+        <v>0</v>
+      </c>
+      <c r="F93" s="2">
         <v>1.062728121551651E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94">
+    <row r="94" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="2">
         <v>93</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C94" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D94">
+      <c r="D94" s="2">
         <v>0.37297036853779231</v>
       </c>
-      <c r="E94">
+      <c r="E94" s="2">
         <v>0.61087137170631467</v>
       </c>
-      <c r="F94">
+      <c r="F94" s="2">
         <v>0.4651838423616203</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95">
+    <row r="95" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="2">
         <v>94</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C95" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D95">
+      <c r="D95" s="2">
         <v>3.9178623072959502E-2</v>
       </c>
-      <c r="E95">
-        <v>0.21597159472199859</v>
-      </c>
-      <c r="F95">
+      <c r="E95" s="2">
+        <v>5.5054346394627217E-2</v>
+      </c>
+      <c r="F95" s="2">
         <v>7.9566521871286017E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96">
+    <row r="96" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="2">
         <v>95</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C96" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D96">
+      <c r="D96" s="2">
         <v>0.10431461648936741</v>
       </c>
-      <c r="E96">
+      <c r="E96" s="2">
         <v>0.30156302587762979</v>
       </c>
-      <c r="F96">
+      <c r="F96" s="2">
         <v>-1.061170270933302E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97">
+    <row r="97" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="2">
         <v>96</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C97" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D97">
+      <c r="D97" s="2">
         <v>-7.3846271430611662E-2</v>
       </c>
-      <c r="E97">
+      <c r="E97" s="2">
         <v>-0.13343351593185249</v>
       </c>
-      <c r="F97">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98">
+      <c r="F97" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="2">
         <v>97</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C98" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D98">
+      <c r="D98" s="2">
         <v>4.123570864451017E-2</v>
       </c>
-      <c r="E98">
+      <c r="E98" s="2">
         <v>0.18586739785166589</v>
       </c>
-      <c r="F98">
+      <c r="F98" s="2">
         <v>0.1529037461966696</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99">
+    <row r="99" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="2">
         <v>98</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C99" t="s">
+      <c r="C99" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D99">
+      <c r="D99" s="2">
         <v>5.1456439656485539E-2</v>
       </c>
-      <c r="E99">
-        <v>0</v>
-      </c>
-      <c r="F99">
+      <c r="E99" s="2">
+        <v>0</v>
+      </c>
+      <c r="F99" s="2">
         <v>6.3687293099057796E-2</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100">
+    <row r="100" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="2">
         <v>99</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C100" t="s">
+      <c r="C100" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D100">
+      <c r="D100" s="2">
         <v>4.1200432556821903E-2</v>
       </c>
-      <c r="E100">
-        <v>0</v>
-      </c>
-      <c r="F100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101">
+      <c r="E100" s="2">
+        <v>0</v>
+      </c>
+      <c r="F100" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="2">
         <v>100</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C101" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D101">
+      <c r="D101" s="2">
         <v>-2.6957011111411789E-2</v>
       </c>
-      <c r="E101">
-        <v>-1.7647058823529319E-3</v>
-      </c>
-      <c r="F101">
+      <c r="E101" s="2">
+        <v>0.12470588235294119</v>
+      </c>
+      <c r="F101" s="2">
         <v>-1.1359243390843749E-3</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102">
+    <row r="102" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="2">
         <v>101</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C102" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D102">
-        <v>2.515685105602683E-2</v>
-      </c>
-      <c r="E102">
-        <v>7.4953763787098754E-2</v>
-      </c>
-      <c r="F102">
-        <v>3.4803156195610967E-2</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103">
+      <c r="D102" s="2">
+        <v>-2.155691623602296E-3</v>
+      </c>
+      <c r="E102" s="2">
+        <v>3.2600822610628168E-2</v>
+      </c>
+      <c r="F102" s="2">
+        <v>3.9194880387102143E-3</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="2">
         <v>102</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C103" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D103">
+      <c r="D103" s="2">
         <v>-3.2550790108991631E-2</v>
       </c>
-      <c r="E103">
-        <v>0</v>
-      </c>
-      <c r="F103">
+      <c r="E103" s="2">
+        <v>0</v>
+      </c>
+      <c r="F103" s="2">
         <v>2.691808323393257E-2</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104">
+    <row r="104" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="2">
         <v>103</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C104" t="s">
+      <c r="C104" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D104">
-        <v>6.6145224046129963E-2</v>
-      </c>
-      <c r="E104">
-        <v>3.3921568627450979E-2</v>
-      </c>
-      <c r="F104">
+      <c r="D104" s="2">
+        <v>2.6597364498270409E-2</v>
+      </c>
+      <c r="E104" s="2">
+        <v>-3.3921568627450979E-2</v>
+      </c>
+      <c r="F104" s="2">
         <v>-3.1056786350904E-2</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105">
+    <row r="105" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="2">
         <v>104</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C105" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D105">
+      <c r="D105" s="2">
         <v>3.8685708659506407E-2</v>
       </c>
-      <c r="E105">
-        <v>0</v>
-      </c>
-      <c r="F105">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106">
+      <c r="E105" s="2">
+        <v>0</v>
+      </c>
+      <c r="F105" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="2">
         <v>105</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C106" t="s">
+      <c r="C106" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D106">
+      <c r="D106" s="2">
         <v>3.185125257671656E-2</v>
       </c>
-      <c r="E106">
+      <c r="E106" s="2">
         <v>-3.7450980392156857E-2</v>
       </c>
-      <c r="F106">
+      <c r="F106" s="2">
         <v>2.9223325693913931E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107">
+    <row r="107" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="2">
         <v>106</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C107" t="s">
+      <c r="C107" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D107">
+      <c r="D107" s="2">
         <v>-4.2827998513518498E-2</v>
       </c>
-      <c r="E107">
+      <c r="E107" s="2">
         <v>0.1085550445753202</v>
       </c>
-      <c r="F107">
+      <c r="F107" s="2">
         <v>-6.0204952772686671E-3</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108">
+    <row r="108" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="2">
         <v>107</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C108" t="s">
+      <c r="C108" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D108">
+      <c r="D108" s="2">
         <v>9.6914869452768039E-3</v>
       </c>
-      <c r="E108">
+      <c r="E108" s="2">
         <v>4.2773047454949503E-2</v>
       </c>
-      <c r="F108">
+      <c r="F108" s="2">
         <v>2.729418626706109E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109">
+    <row r="109" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="2">
         <v>108</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C109" t="s">
+      <c r="C109" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D109">
+      <c r="D109" s="2">
         <v>7.8601990289410867E-2</v>
       </c>
-      <c r="E109">
+      <c r="E109" s="2">
         <v>3.3734059950144911E-2</v>
       </c>
-      <c r="F109">
+      <c r="F109" s="2">
         <v>2.3667402314168182E-2</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110">
+    <row r="110" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="2">
         <v>109</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C110" t="s">
+      <c r="C110" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D110">
+      <c r="D110" s="2">
         <v>8.6024531024531031E-2</v>
       </c>
-      <c r="E110">
-        <v>0</v>
-      </c>
-      <c r="F110">
+      <c r="E110" s="2">
+        <v>0</v>
+      </c>
+      <c r="F110" s="2">
         <v>7.8716577540106955E-2</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111">
+    <row r="111" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="2">
         <v>110</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C111" t="s">
+      <c r="C111" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D111">
+      <c r="D111" s="2">
         <v>7.0437987306130601E-2</v>
       </c>
-      <c r="E111">
+      <c r="E111" s="2">
         <v>-3.9019607843137259E-2</v>
       </c>
-      <c r="F111">
+      <c r="F111" s="2">
         <v>0.12692891747334811</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112">
+    <row r="112" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="2">
         <v>111</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C112" t="s">
+      <c r="C112" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D112">
+      <c r="D112" s="2">
         <v>0.1103800522531953</v>
       </c>
-      <c r="E112">
+      <c r="E112" s="2">
         <v>0.1892156862745098</v>
       </c>
-      <c r="F112">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113">
+      <c r="F112" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="2">
         <v>112</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C113" t="s">
+      <c r="C113" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D113">
+      <c r="D113" s="2">
         <v>-1.004248472071873E-2</v>
       </c>
-      <c r="E113">
-        <v>0</v>
-      </c>
-      <c r="F113">
+      <c r="E113" s="2">
+        <v>0</v>
+      </c>
+      <c r="F113" s="2">
         <v>-0.12351165055488129</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114">
+    <row r="114" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="2">
         <v>113</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C114" t="s">
+      <c r="C114" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D114">
-        <v>0</v>
-      </c>
-      <c r="E114">
+      <c r="D114" s="2">
+        <v>0</v>
+      </c>
+      <c r="E114" s="2">
         <v>-0.21617647058823519</v>
       </c>
-      <c r="F114">
+      <c r="F114" s="2">
         <v>-7.0511841100076383E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115">
+    <row r="115" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="2">
         <v>114</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C115" t="s">
+      <c r="C115" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D115">
+      <c r="D115" s="2">
         <v>-2.119278136930108E-2</v>
       </c>
-      <c r="E115">
+      <c r="E115" s="2">
         <v>-6.535947712418301E-2</v>
       </c>
-      <c r="F115">
+      <c r="F115" s="2">
         <v>-7.9483232575278673E-3</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116">
+    <row r="116" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="2">
         <v>115</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C116" t="s">
+      <c r="C116" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D116">
-        <v>0</v>
-      </c>
-      <c r="E116">
+      <c r="D116" s="2">
+        <v>0</v>
+      </c>
+      <c r="E116" s="2">
         <v>0.23338001400466829</v>
       </c>
-      <c r="F116">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117">
+      <c r="F116" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="2">
         <v>116</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C117" t="s">
+      <c r="C117" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D117">
+      <c r="D117" s="2">
         <v>0.1154329935156045</v>
       </c>
-      <c r="E117">
-        <v>0</v>
-      </c>
-      <c r="F117">
+      <c r="E117" s="2">
+        <v>0</v>
+      </c>
+      <c r="F117" s="2">
         <v>7.3720397249809014E-2</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118">
+    <row r="118" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="2">
         <v>117</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C118" t="s">
+      <c r="C118" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D118">
+      <c r="D118" s="2">
         <v>9.135380580461111E-2</v>
       </c>
-      <c r="E118">
-        <v>0</v>
-      </c>
-      <c r="F118">
+      <c r="E118" s="2">
+        <v>0</v>
+      </c>
+      <c r="F118" s="2">
         <v>8.7632628809099389E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119">
+    <row r="119" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="2">
         <v>118</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C119" t="s">
+      <c r="C119" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D119">
-        <v>0</v>
-      </c>
-      <c r="E119">
-        <v>0</v>
-      </c>
-      <c r="F119">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120">
+      <c r="D119" s="2">
+        <v>0</v>
+      </c>
+      <c r="E119" s="2">
+        <v>0</v>
+      </c>
+      <c r="F119" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="2">
         <v>119</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C120" t="s">
+      <c r="C120" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D120">
-        <v>0</v>
-      </c>
-      <c r="E120">
-        <v>0</v>
-      </c>
-      <c r="F120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121">
+      <c r="D120" s="2">
+        <v>0</v>
+      </c>
+      <c r="E120" s="2">
+        <v>0</v>
+      </c>
+      <c r="F120" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="2">
         <v>120</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C121" t="s">
+      <c r="C121" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D121">
-        <v>0</v>
-      </c>
-      <c r="E121">
+      <c r="D121" s="2">
+        <v>0</v>
+      </c>
+      <c r="E121" s="2">
         <v>0.2009803921568627</v>
       </c>
-      <c r="F121">
+      <c r="F121" s="2">
         <v>0.25174433409727531</v>
       </c>
     </row>
